--- a/sub_pro_16_wc_2026_pred/datasets/tsi_2_prediction.xlsx
+++ b/sub_pro_16_wc_2026_pred/datasets/tsi_2_prediction.xlsx
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.2359813176626005</v>
+        <v>0.2342949047852232</v>
       </c>
     </row>
     <row r="3">
@@ -398,7 +398,7 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.9383790825617916</v>
+        <v>-0.9406332345516335</v>
       </c>
     </row>
     <row r="4">
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.201357590275237</v>
+        <v>-0.204698430589822</v>
       </c>
     </row>
     <row r="5">
@@ -428,7 +428,7 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.4597494271900827</v>
+        <v>-0.4637575336615361</v>
       </c>
     </row>
     <row r="6">
@@ -443,7 +443,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.2136832366529799</v>
+        <v>-0.219985777510685</v>
       </c>
     </row>
     <row r="7">
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.8059456543298233</v>
+        <v>-0.8096266350551489</v>
       </c>
     </row>
     <row r="8">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.9920586123491776</v>
+        <v>-0.9925231830781639</v>
       </c>
     </row>
     <row r="9">
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.3109611469152784</v>
+        <v>0.3065822401229708</v>
       </c>
     </row>
     <row r="10">
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="C10">
-        <v>1.203212879120572</v>
+        <v>1.202283506980997</v>
       </c>
     </row>
     <row r="11">
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.3991108635731037</v>
+        <v>0.3968510945061324</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.9902792495712347</v>
+        <v>-0.9912950862046768</v>
       </c>
     </row>
     <row r="13">
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C13">
-        <v>-0.3153064894059182</v>
+        <v>-0.3191898276379563</v>
       </c>
     </row>
     <row r="14">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.3513430483097437</v>
+        <v>0.3475037768677302</v>
       </c>
     </row>
     <row r="15">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.2032019597466009</v>
+        <v>-0.2044065594512369</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="C16">
-        <v>-0.2358845178387708</v>
+        <v>-0.1150299965566823</v>
       </c>
     </row>
     <row r="17">
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.1807421590952332</v>
+        <v>0.177292078184343</v>
       </c>
     </row>
     <row r="18">
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>0.8071142602457819</v>
+        <v>0.8032880958363193</v>
       </c>
     </row>
     <row r="19">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>-1.119875610154607</v>
+        <v>-1.120259108673919</v>
       </c>
     </row>
     <row r="20">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>-0.09599161222893357</v>
+        <v>-0.09666898389283185</v>
       </c>
     </row>
     <row r="21">
@@ -668,7 +668,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>0.2268234713402441</v>
+        <v>0.2251646783875827</v>
       </c>
     </row>
     <row r="22">
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="C22">
-        <v>0.8308919423192251</v>
+        <v>0.8272425795971851</v>
       </c>
     </row>
     <row r="23">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="C23">
-        <v>0.3131554354536941</v>
+        <v>0.3081561564180899</v>
       </c>
     </row>
     <row r="24">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="C24">
-        <v>-0.2595719416241865</v>
+        <v>-0.2645484806430691</v>
       </c>
     </row>
     <row r="25">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C25">
-        <v>-0.6352539637857013</v>
+        <v>-0.6370817798161449</v>
       </c>
     </row>
     <row r="26">
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="C26">
-        <v>0.5302082214334137</v>
+        <v>0.526589647695752</v>
       </c>
     </row>
     <row r="27">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C27">
-        <v>-0.3504868196430979</v>
+        <v>-0.3518434796232236</v>
       </c>
     </row>
     <row r="28">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="C28">
-        <v>-0.2491268039756448</v>
+        <v>-0.2513599661949076</v>
       </c>
     </row>
     <row r="29">
@@ -788,7 +788,7 @@
         </is>
       </c>
       <c r="C29">
-        <v>-1.074457541874035</v>
+        <v>-1.078118990652995</v>
       </c>
     </row>
     <row r="30">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="C30">
-        <v>1.746295107738242</v>
+        <v>1.743103371292758</v>
       </c>
     </row>
     <row r="31">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="C31">
-        <v>-0.8355436274537638</v>
+        <v>-0.8370003531004393</v>
       </c>
     </row>
     <row r="32">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="C32">
-        <v>-0.8365978387767411</v>
+        <v>-0.8374451481182319</v>
       </c>
     </row>
     <row r="33">
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="C33">
-        <v>0.2882036984301447</v>
+        <v>0.2859163715692081</v>
       </c>
     </row>
     <row r="34">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="C34">
-        <v>1.839249935134412</v>
+        <v>1.835806438806084</v>
       </c>
     </row>
     <row r="35">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="C35">
-        <v>0.3581205286286003</v>
+        <v>0.3578264838286386</v>
       </c>
     </row>
     <row r="36">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="C36">
-        <v>-0.7068218600963386</v>
+        <v>-0.7082084965529271</v>
       </c>
     </row>
     <row r="37">
@@ -908,7 +908,7 @@
         </is>
       </c>
       <c r="C37">
-        <v>0.2910334512645891</v>
+        <v>0.2858734209984232</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38">
-        <v>1.34180657118504</v>
+        <v>1.338674122736296</v>
       </c>
     </row>
     <row r="39">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C39">
-        <v>-0.1236070673775305</v>
+        <v>-0.1248703635535452</v>
       </c>
     </row>
     <row r="40">
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="C40">
-        <v>-0.021021811042347</v>
+        <v>-0.02522999336365488</v>
       </c>
     </row>
     <row r="41">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="C41">
-        <v>-0.7725655434801525</v>
+        <v>-0.7744830129470184</v>
       </c>
     </row>
     <row r="42">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="C42">
-        <v>1.138850849943402</v>
+        <v>1.136173937582896</v>
       </c>
     </row>
     <row r="43">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="C43">
-        <v>-0.4224188478158291</v>
+        <v>-0.4235437891351658</v>
       </c>
     </row>
     <row r="44">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="C44">
-        <v>-0.6198648382210685</v>
+        <v>-0.6230606790180957</v>
       </c>
     </row>
     <row r="45">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C45">
-        <v>0.4983409962789783</v>
+        <v>0.4973349707640076</v>
       </c>
     </row>
     <row r="46">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="C46">
-        <v>1.396457271382261</v>
+        <v>1.392565486019112</v>
       </c>
     </row>
     <row r="47">
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="C47">
-        <v>0.3484918070302599</v>
+        <v>0.3451060197708897</v>
       </c>
     </row>
     <row r="48">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="C48">
-        <v>-0.825625102938947</v>
+        <v>-0.8261460681069039</v>
       </c>
     </row>
     <row r="49">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C49">
-        <v>-0.3317183120742866</v>
+        <v>-0.3326144250600329</v>
       </c>
     </row>
   </sheetData>
